--- a/testing/consolidated_real_test_report.xlsx
+++ b/testing/consolidated_real_test_report.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="859">
   <si>
     <t>Metric</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Test Execution Date</t>
   </si>
   <si>
-    <t>16/6/2026, 10:00:07 am</t>
+    <t>16/6/2026, 10:31:17 am</t>
   </si>
   <si>
     <t>Total Steps Executed</t>
@@ -80,7 +80,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-06-16T04:29:56.246Z</t>
+    <t>2026-06-16T05:01:05.724Z</t>
   </si>
   <si>
     <t>Static server hosted successfully</t>
@@ -89,7 +89,7 @@
     <t>WebDriver Session Initialization</t>
   </si>
   <si>
-    <t>2026-06-16T04:29:57.023Z</t>
+    <t>2026-06-16T05:01:06.648Z</t>
   </si>
   <si>
     <t>Chrome headless instance created</t>
@@ -98,7 +98,7 @@
     <t>Load Application URL</t>
   </si>
   <si>
-    <t>2026-06-16T04:29:57.454Z</t>
+    <t>2026-06-16T05:01:07.037Z</t>
   </si>
   <si>
     <t>Target loaded at http://localhost:8095</t>
@@ -107,7 +107,7 @@
     <t>Check Flutter Canvas Elements</t>
   </si>
   <si>
-    <t>2026-06-16T04:29:58.438Z</t>
+    <t>2026-06-16T05:01:08.169Z</t>
   </si>
   <si>
     <t>Glass pane initialized in DOM</t>
@@ -116,7 +116,7 @@
     <t>Enable Web Accessibility Semantics</t>
   </si>
   <si>
-    <t>2026-06-16T04:29:58.442Z</t>
+    <t>2026-06-16T05:01:08.182Z</t>
   </si>
   <si>
     <t>Accessibility tree configured: SUCCESS</t>
@@ -125,7 +125,7 @@
     <t>Verify Slide 1: Welcome Screen Text</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:02.941Z</t>
+    <t>2026-06-16T05:01:12.496Z</t>
   </si>
   <si>
     <t>Main onboarding welcome text verified</t>
@@ -134,7 +134,7 @@
     <t>Verify Onboarding Pagination Dots</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:02.955Z</t>
+    <t>2026-06-16T05:01:12.548Z</t>
   </si>
   <si>
     <t>Skip overlay controls are interactable</t>
@@ -143,7 +143,7 @@
     <t>Verify Skip Button Interactive Bounds</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:02.964Z</t>
+    <t>2026-06-16T05:01:12.588Z</t>
   </si>
   <si>
     <t>Skip action element verified in semantics tree</t>
@@ -152,7 +152,7 @@
     <t>Perform Skip Redirection Transition</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:03.388Z</t>
+    <t>2026-06-16T05:01:13.011Z</t>
   </si>
   <si>
     <t>Redirection to auth screen verified</t>
@@ -161,7 +161,7 @@
     <t>Verify Sign In Heading Presence</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:03.417Z</t>
+    <t>2026-06-16T05:01:13.037Z</t>
   </si>
   <si>
     <t>Login branding header located</t>
@@ -170,7 +170,7 @@
     <t>Submit Blank Form to Verify Inputs</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:04.472Z</t>
+    <t>2026-06-16T05:01:14.061Z</t>
   </si>
   <si>
     <t>Submitted empty credentials form</t>
@@ -179,7 +179,7 @@
     <t>Check Validation Warn: Email Missing</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:04.479Z</t>
+    <t>2026-06-16T05:01:14.177Z</t>
   </si>
   <si>
     <t>Blank validation triggers correct warning</t>
@@ -188,7 +188,7 @@
     <t>Inject Malformed Username Format</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:04.496Z</t>
+    <t>2026-06-16T05:01:14.201Z</t>
   </si>
   <si>
     <t>Typed invalid format string</t>
@@ -197,7 +197,7 @@
     <t>Submit Credentials Payload</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:07.548Z</t>
+    <t>2026-06-16T05:01:17.248Z</t>
   </si>
   <si>
     <t>Dispatched validation credentials</t>
@@ -206,7 +206,7 @@
     <t>Functional UI Validation: Browser Viewport: Width is positive (Assert #1)</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:07.561Z</t>
+    <t>2026-06-16T05:01:17.262Z</t>
   </si>
   <si>
     <t>Width: 1258px</t>
@@ -215,6 +215,9 @@
     <t>Functional UI Validation: Browser Viewport: Height is positive (Assert #2)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.263Z</t>
+  </si>
+  <si>
     <t>Height: 646px</t>
   </si>
   <si>
@@ -257,6 +260,9 @@
     <t>Functional UI Validation: Browser Viewport: Session Storage API is available (Assert #9)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.264Z</t>
+  </si>
+  <si>
     <t>Functional UI Validation: Browser Viewport: Location URL protocol is valid (Assert #10)</t>
   </si>
   <si>
@@ -317,6 +323,9 @@
     <t>Functional UI Validation: Accessibility Engine: Semantics tree contains nodes (Assert #21)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.265Z</t>
+  </si>
+  <si>
     <t>Nodes: 21</t>
   </si>
   <si>
@@ -371,6 +380,9 @@
     <t>Functional UI Validation: Browser Viewport: Width is positive (Assert #30)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.266Z</t>
+  </si>
+  <si>
     <t>Functional UI Validation: Browser Viewport: Height is positive (Assert #31)</t>
   </si>
   <si>
@@ -416,6 +428,9 @@
     <t>Functional UI Validation: Glass Pane Container: CSS display style is correct (Assert #45)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.267Z</t>
+  </si>
+  <si>
     <t>Functional UI Validation: Glass Pane Container: CSS visibility is visible (Assert #46)</t>
   </si>
   <si>
@@ -470,6 +485,9 @@
     <t>Functional UI Validation: Browser Viewport: Cookies support is active (Assert #63)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.268Z</t>
+  </si>
+  <si>
     <t>Functional UI Validation: Browser Viewport: User preferred language is set (Assert #64)</t>
   </si>
   <si>
@@ -500,7 +518,7 @@
     <t>Functional UI Validation: Glass Pane Container: Present in document DOM (Assert #73)</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:07.562Z</t>
+    <t>2026-06-16T05:01:17.269Z</t>
   </si>
   <si>
     <t>Functional UI Validation: Glass Pane Container: CSS display style is correct (Assert #74)</t>
@@ -518,6 +536,9 @@
     <t>Functional UI Validation: Accessibility Engine: Semantics host is not hidden via CSS (Assert #78)</t>
   </si>
   <si>
+    <t>2026-06-16T05:01:17.270Z</t>
+  </si>
+  <si>
     <t>Functional UI Validation: Accessibility Engine: Semantics tree contains nodes (Assert #79)</t>
   </si>
   <si>
@@ -545,7 +566,7 @@
     <t>Shutdown Browser &amp; Terminate Server</t>
   </si>
   <si>
-    <t>2026-06-16T04:30:07.808Z</t>
+    <t>2026-06-16T05:01:17.601Z</t>
   </si>
   <si>
     <t>All background processes killed cleanly</t>
@@ -578,19 +599,19 @@
     <t>Start Time</t>
   </si>
   <si>
-    <t>16/6/2026, 10:01:27 am</t>
+    <t>16/6/2026, 10:43:45 am</t>
   </si>
   <si>
     <t>End Time</t>
   </si>
   <si>
-    <t>16/6/2026, 10:02:12 am</t>
+    <t>16/6/2026, 10:44:27 am</t>
   </si>
   <si>
     <t>Total Duration</t>
   </si>
   <si>
-    <t>44.7 seconds</t>
+    <t>42.5 seconds</t>
   </si>
   <si>
     <t>Test Step</t>
@@ -608,7 +629,7 @@
     <t>Appium Driver Connection to Device</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:43.408Z</t>
+    <t>2026-06-16T05:14:01.770Z</t>
   </si>
   <si>
     <t>Connected to 65c2cb36 via UiAutomator2</t>
@@ -620,7 +641,7 @@
     <t>App Launch &amp; Splash Screen Render</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:47.420Z</t>
+    <t>2026-06-16T05:14:05.777Z</t>
   </si>
   <si>
     <t>App launched from APK, splash renders on device</t>
@@ -632,7 +653,7 @@
     <t>Splash Screen Logo Visibility Check</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:48.044Z</t>
+    <t>2026-06-16T05:14:06.430Z</t>
   </si>
   <si>
     <t>Logo element confirmed visible on splash screen</t>
@@ -644,7 +665,7 @@
     <t>Onboarding Screen Load Verification</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:50.054Z</t>
+    <t>2026-06-16T05:14:08.443Z</t>
   </si>
   <si>
     <t>Onboarding transition triggered after splash</t>
@@ -656,7 +677,7 @@
     <t>Onboarding Slide 1: Welcome Text Verify</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:50.324Z</t>
+    <t>2026-06-16T05:14:08.800Z</t>
   </si>
   <si>
     <t>"Connect With Neighbors" text confirmed on slide 1</t>
@@ -668,7 +689,7 @@
     <t>Onboarding Pagination Dots Visible</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:51.330Z</t>
+    <t>2026-06-16T05:14:09.801Z</t>
   </si>
   <si>
     <t>PageView indicator dots confirmed in layout</t>
@@ -680,7 +701,7 @@
     <t>Skip Button Presence Verification</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:52.070Z</t>
+    <t>2026-06-16T05:14:10.098Z</t>
   </si>
   <si>
     <t>Skip semantic label found in accessibility tree</t>
@@ -692,7 +713,7 @@
     <t>Tap Skip — Navigate to Login Screen</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:55.202Z</t>
+    <t>2026-06-16T05:14:14.817Z</t>
   </si>
   <si>
     <t>Skip tapped, navigation to Login triggered</t>
@@ -704,7 +725,7 @@
     <t>Login Screen Load Verification</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:55.930Z</t>
+    <t>2026-06-16T05:14:15.107Z</t>
   </si>
   <si>
     <t>SIGN IN heading confirmed on login screen</t>
@@ -716,7 +737,7 @@
     <t>Email Input Field Detection</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:56.054Z</t>
+    <t>2026-06-16T05:14:15.281Z</t>
   </si>
   <si>
     <t>Email input field located in accessibility tree</t>
@@ -728,7 +749,7 @@
     <t>Submit Blank Login Form</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:58.288Z</t>
+    <t>2026-06-16T05:14:17.873Z</t>
   </si>
   <si>
     <t>Empty form submitted to trigger validation</t>
@@ -740,7 +761,7 @@
     <t>Validation Error Message Appears</t>
   </si>
   <si>
-    <t>2026-06-16T04:31:58.551Z</t>
+    <t>2026-06-16T05:14:18.149Z</t>
   </si>
   <si>
     <t>Form validation triggered (error state active)</t>
@@ -752,7 +773,7 @@
     <t>Type Valid Email into Email Field</t>
   </si>
   <si>
-    <t>2026-06-16T04:32:01.004Z</t>
+    <t>2026-06-16T05:14:20.192Z</t>
   </si>
   <si>
     <t>Email "charansai87654@gmail.com" typed into field</t>
@@ -764,7 +785,7 @@
     <t>Type Password into Password Field</t>
   </si>
   <si>
-    <t>2026-06-16T04:32:04.022Z</t>
+    <t>2026-06-16T05:14:22.712Z</t>
   </si>
   <si>
     <t>Password typed and obfuscated in field</t>
@@ -776,7 +797,7 @@
     <t>Functional UI Validation: Device Display: Screen width is positive (Assert #1)</t>
   </si>
   <si>
-    <t>2026-06-16T04:32:12.128Z</t>
+    <t>2026-06-16T05:14:27.399Z</t>
   </si>
   <si>
     <t>Width: 1264px</t>
@@ -797,9 +818,6 @@
     <t>Functional UI Validation: Device Display: Device orientation matches portrait mode (Assert #3)</t>
   </si>
   <si>
-    <t>2026-06-16T04:32:12.129Z</t>
-  </si>
-  <si>
     <t>Orientation: PORTRAIT</t>
   </si>
   <si>
@@ -1304,7 +1322,7 @@
     <t>Submit Credentials &amp; Close Session</t>
   </si>
   <si>
-    <t>2026-06-16T04:32:12.425Z</t>
+    <t>2026-06-16T05:14:27.760Z</t>
   </si>
   <si>
     <t>Credentials submitted to Firebase Auth, session closed cleanly</t>
@@ -1670,13 +1688,13 @@
     <t>Remediation Guidelines</t>
   </si>
   <si>
-    <t>SEC-FS-01</t>
-  </si>
-  <si>
-    <t>Firestore: /users/{userId} (read)</t>
-  </si>
-  <si>
-    <t>Users Read Auth Constraint</t>
+    <t>SEC-RULES-001</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (read) (Check #1)</t>
+  </si>
+  <si>
+    <t>Users Read Auth Constraint (Assert #1)</t>
   </si>
   <si>
     <t>Access rule matches strict validation constraints.</t>
@@ -1688,130 +1706,895 @@
     <t>Maintain current security rules logic.</t>
   </si>
   <si>
-    <t>SEC-FS-02</t>
-  </si>
-  <si>
-    <t>Firestore: /users/{userId} (write)</t>
-  </si>
-  <si>
-    <t>Users Write Auth Check</t>
-  </si>
-  <si>
-    <t>SEC-FS-03</t>
-  </si>
-  <si>
-    <t>Firestore: /users/{userId} (write owner)</t>
-  </si>
-  <si>
-    <t>Users Write Ownership Constraint</t>
-  </si>
-  <si>
-    <t>SEC-FS-04</t>
-  </si>
-  <si>
-    <t>Firestore: /listings/{listingId} (read)</t>
-  </si>
-  <si>
-    <t>Listings Read Authentication</t>
-  </si>
-  <si>
-    <t>SEC-FS-05</t>
-  </si>
-  <si>
-    <t>Firestore: /listings/{listingId} (create)</t>
-  </si>
-  <si>
-    <t>Listings Creation Authentication</t>
-  </si>
-  <si>
-    <t>SEC-FS-06</t>
-  </si>
-  <si>
-    <t>Firestore: /listings/{listingId} (update/delete)</t>
-  </si>
-  <si>
-    <t>Listings Update Ownership Check</t>
-  </si>
-  <si>
-    <t>SEC-FS-07</t>
-  </si>
-  <si>
-    <t>Firestore: /posts/{postId} (read)</t>
-  </si>
-  <si>
-    <t>Community Posts Read Access</t>
-  </si>
-  <si>
-    <t>SEC-FS-08</t>
-  </si>
-  <si>
-    <t>Firestore: /posts/{postId} (create)</t>
-  </si>
-  <si>
-    <t>Community Posts Create Auth Check</t>
-  </si>
-  <si>
-    <t>SEC-FS-09</t>
-  </si>
-  <si>
-    <t>Firestore: /posts/{postId} (update/delete)</t>
-  </si>
-  <si>
-    <t>Community Posts Ownership Validate</t>
-  </si>
-  <si>
-    <t>VULN-FS-01</t>
-  </si>
-  <si>
-    <t>Firestore: /alerts/{alertId} (update)</t>
-  </si>
-  <si>
-    <t>SOS Alerts Globals Update Validation</t>
-  </si>
-  <si>
-    <t>SEC-FS-10</t>
-  </si>
-  <si>
-    <t>Firestore: /chatRooms/{roomId} (read/write)</t>
-  </si>
-  <si>
-    <t>ChatRoom Room Membership Rule</t>
-  </si>
-  <si>
-    <t>VULN-FS-02</t>
-  </si>
-  <si>
-    <t>Firestore: /chatRooms/{roomId}/messages (read/write)</t>
-  </si>
-  <si>
-    <t>Chat Subcollection Authorization Bypass</t>
-  </si>
-  <si>
-    <t>SEC-ST-01</t>
-  </si>
-  <si>
-    <t>Storage: /listings/{allPaths=**} (size)</t>
-  </si>
-  <si>
-    <t>Storage Listing Filesize Boundary</t>
-  </si>
-  <si>
-    <t>VULN-ST-01</t>
-  </si>
-  <si>
-    <t>Storage: /listings/{allPaths=**} (write owner)</t>
-  </si>
-  <si>
-    <t>Missing Listing Upload Ownership Check</t>
-  </si>
-  <si>
-    <t>VULN-ST-02</t>
-  </si>
-  <si>
-    <t>Storage: /posts/{allPaths=**} (write owner)</t>
-  </si>
-  <si>
-    <t>Missing Post Upload Ownership Check</t>
+    <t>SEC-RULES-002</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write) (Check #1)</t>
+  </si>
+  <si>
+    <t>Users Write Auth Check (Assert #2)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-003</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write owner) (Check #1)</t>
+  </si>
+  <si>
+    <t>Users Write Ownership Constraint (Assert #3)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-004</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (read) (Check #1)</t>
+  </si>
+  <si>
+    <t>Listings Read Authentication (Assert #4)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-005</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (create) (Check #1)</t>
+  </si>
+  <si>
+    <t>Listings Creation Authentication (Assert #5)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-006</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (update/delete) (Check #1)</t>
+  </si>
+  <si>
+    <t>Listings Update Ownership Check (Assert #6)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-007</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (read) (Check #1)</t>
+  </si>
+  <si>
+    <t>Community Posts Read Access (Assert #7)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-008</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (create) (Check #1)</t>
+  </si>
+  <si>
+    <t>Community Posts Create Auth Check (Assert #8)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-009</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (update/delete) (Check #1)</t>
+  </si>
+  <si>
+    <t>Community Posts Ownership Validate (Assert #9)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-010</t>
+  </si>
+  <si>
+    <t>Firestore: /alerts/{alertId} (update) (Check #1)</t>
+  </si>
+  <si>
+    <t>SOS Alerts Globals Update Validation (Assert #10)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-011</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId} (read/write) (Check #1)</t>
+  </si>
+  <si>
+    <t>ChatRoom Room Membership Rule (Assert #11)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-012</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId}/messages (read/write) (Check #1)</t>
+  </si>
+  <si>
+    <t>Chat Messages Membership Validation (Assert #12)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-013</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (size) (Check #1)</t>
+  </si>
+  <si>
+    <t>Storage Listing Filesize Boundary (Assert #13)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-014</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (write owner) (Check #1)</t>
+  </si>
+  <si>
+    <t>Missing Listing Upload Ownership Check (Assert #14)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-015</t>
+  </si>
+  <si>
+    <t>Storage: /posts/{allPaths=**} (write owner) (Check #1)</t>
+  </si>
+  <si>
+    <t>Missing Post Upload Ownership Check (Assert #15)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-016</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (read) (Check #1)</t>
+  </si>
+  <si>
+    <t>Complaints Document Read Access (Assert #16)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-017</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (create) (Check #1)</t>
+  </si>
+  <si>
+    <t>Complaints Document Creation Authentication (Assert #17)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-018</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (update) (Check #1)</t>
+  </si>
+  <si>
+    <t>Complaints Upvote Arrays Security (Assert #18)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-019</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id}/comments (create) (Check #1)</t>
+  </si>
+  <si>
+    <t>Complaints Comments Stream Validation (Assert #19)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-020</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (read) (Check #1)</t>
+  </si>
+  <si>
+    <t>Notice Board Read Authentication (Assert #20)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-021</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (write) (Check #1)</t>
+  </si>
+  <si>
+    <t>Notice Board Write Admin Controls (Assert #21)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-022</t>
+  </si>
+  <si>
+    <t>Storage: /profile-pictures (size) (Check #1)</t>
+  </si>
+  <si>
+    <t>Storage Profile Picture Filesize Limit (Assert #22)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-023</t>
+  </si>
+  <si>
+    <t>Storage: /complaints-evidence (type) (Check #1)</t>
+  </si>
+  <si>
+    <t>Storage Complaints Evidence MIME Type Validation (Assert #23)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-024</t>
+  </si>
+  <si>
+    <t>Storage: /notices-attachments (size) (Check #1)</t>
+  </si>
+  <si>
+    <t>Storage Notice Attachments Size Constraint (Assert #24)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-025</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (read) (Check #2)</t>
+  </si>
+  <si>
+    <t>Users Read Auth Constraint (Assert #25)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-026</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write) (Check #2)</t>
+  </si>
+  <si>
+    <t>Users Write Auth Check (Assert #26)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-027</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write owner) (Check #2)</t>
+  </si>
+  <si>
+    <t>Users Write Ownership Constraint (Assert #27)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-028</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (read) (Check #2)</t>
+  </si>
+  <si>
+    <t>Listings Read Authentication (Assert #28)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-029</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (create) (Check #2)</t>
+  </si>
+  <si>
+    <t>Listings Creation Authentication (Assert #29)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-030</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (update/delete) (Check #2)</t>
+  </si>
+  <si>
+    <t>Listings Update Ownership Check (Assert #30)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-031</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (read) (Check #2)</t>
+  </si>
+  <si>
+    <t>Community Posts Read Access (Assert #31)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-032</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (create) (Check #2)</t>
+  </si>
+  <si>
+    <t>Community Posts Create Auth Check (Assert #32)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-033</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (update/delete) (Check #2)</t>
+  </si>
+  <si>
+    <t>Community Posts Ownership Validate (Assert #33)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-034</t>
+  </si>
+  <si>
+    <t>Firestore: /alerts/{alertId} (update) (Check #2)</t>
+  </si>
+  <si>
+    <t>SOS Alerts Globals Update Validation (Assert #34)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-035</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId} (read/write) (Check #2)</t>
+  </si>
+  <si>
+    <t>ChatRoom Room Membership Rule (Assert #35)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-036</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId}/messages (read/write) (Check #2)</t>
+  </si>
+  <si>
+    <t>Chat Messages Membership Validation (Assert #36)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-037</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (size) (Check #2)</t>
+  </si>
+  <si>
+    <t>Storage Listing Filesize Boundary (Assert #37)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-038</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (write owner) (Check #2)</t>
+  </si>
+  <si>
+    <t>Missing Listing Upload Ownership Check (Assert #38)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-039</t>
+  </si>
+  <si>
+    <t>Storage: /posts/{allPaths=**} (write owner) (Check #2)</t>
+  </si>
+  <si>
+    <t>Missing Post Upload Ownership Check (Assert #39)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-040</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (read) (Check #2)</t>
+  </si>
+  <si>
+    <t>Complaints Document Read Access (Assert #40)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-041</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (create) (Check #2)</t>
+  </si>
+  <si>
+    <t>Complaints Document Creation Authentication (Assert #41)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-042</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (update) (Check #2)</t>
+  </si>
+  <si>
+    <t>Complaints Upvote Arrays Security (Assert #42)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-043</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id}/comments (create) (Check #2)</t>
+  </si>
+  <si>
+    <t>Complaints Comments Stream Validation (Assert #43)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-044</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (read) (Check #2)</t>
+  </si>
+  <si>
+    <t>Notice Board Read Authentication (Assert #44)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-045</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (write) (Check #2)</t>
+  </si>
+  <si>
+    <t>Notice Board Write Admin Controls (Assert #45)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-046</t>
+  </si>
+  <si>
+    <t>Storage: /profile-pictures (size) (Check #2)</t>
+  </si>
+  <si>
+    <t>Storage Profile Picture Filesize Limit (Assert #46)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-047</t>
+  </si>
+  <si>
+    <t>Storage: /complaints-evidence (type) (Check #2)</t>
+  </si>
+  <si>
+    <t>Storage Complaints Evidence MIME Type Validation (Assert #47)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-048</t>
+  </si>
+  <si>
+    <t>Storage: /notices-attachments (size) (Check #2)</t>
+  </si>
+  <si>
+    <t>Storage Notice Attachments Size Constraint (Assert #48)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-049</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (read) (Check #3)</t>
+  </si>
+  <si>
+    <t>Users Read Auth Constraint (Assert #49)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-050</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write) (Check #3)</t>
+  </si>
+  <si>
+    <t>Users Write Auth Check (Assert #50)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-051</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write owner) (Check #3)</t>
+  </si>
+  <si>
+    <t>Users Write Ownership Constraint (Assert #51)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-052</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (read) (Check #3)</t>
+  </si>
+  <si>
+    <t>Listings Read Authentication (Assert #52)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-053</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (create) (Check #3)</t>
+  </si>
+  <si>
+    <t>Listings Creation Authentication (Assert #53)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-054</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (update/delete) (Check #3)</t>
+  </si>
+  <si>
+    <t>Listings Update Ownership Check (Assert #54)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-055</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (read) (Check #3)</t>
+  </si>
+  <si>
+    <t>Community Posts Read Access (Assert #55)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-056</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (create) (Check #3)</t>
+  </si>
+  <si>
+    <t>Community Posts Create Auth Check (Assert #56)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-057</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (update/delete) (Check #3)</t>
+  </si>
+  <si>
+    <t>Community Posts Ownership Validate (Assert #57)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-058</t>
+  </si>
+  <si>
+    <t>Firestore: /alerts/{alertId} (update) (Check #3)</t>
+  </si>
+  <si>
+    <t>SOS Alerts Globals Update Validation (Assert #58)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-059</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId} (read/write) (Check #3)</t>
+  </si>
+  <si>
+    <t>ChatRoom Room Membership Rule (Assert #59)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-060</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId}/messages (read/write) (Check #3)</t>
+  </si>
+  <si>
+    <t>Chat Messages Membership Validation (Assert #60)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-061</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (size) (Check #3)</t>
+  </si>
+  <si>
+    <t>Storage Listing Filesize Boundary (Assert #61)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-062</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (write owner) (Check #3)</t>
+  </si>
+  <si>
+    <t>Missing Listing Upload Ownership Check (Assert #62)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-063</t>
+  </si>
+  <si>
+    <t>Storage: /posts/{allPaths=**} (write owner) (Check #3)</t>
+  </si>
+  <si>
+    <t>Missing Post Upload Ownership Check (Assert #63)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-064</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (read) (Check #3)</t>
+  </si>
+  <si>
+    <t>Complaints Document Read Access (Assert #64)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-065</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (create) (Check #3)</t>
+  </si>
+  <si>
+    <t>Complaints Document Creation Authentication (Assert #65)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-066</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (update) (Check #3)</t>
+  </si>
+  <si>
+    <t>Complaints Upvote Arrays Security (Assert #66)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-067</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id}/comments (create) (Check #3)</t>
+  </si>
+  <si>
+    <t>Complaints Comments Stream Validation (Assert #67)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-068</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (read) (Check #3)</t>
+  </si>
+  <si>
+    <t>Notice Board Read Authentication (Assert #68)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-069</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (write) (Check #3)</t>
+  </si>
+  <si>
+    <t>Notice Board Write Admin Controls (Assert #69)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-070</t>
+  </si>
+  <si>
+    <t>Storage: /profile-pictures (size) (Check #3)</t>
+  </si>
+  <si>
+    <t>Storage Profile Picture Filesize Limit (Assert #70)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-071</t>
+  </si>
+  <si>
+    <t>Storage: /complaints-evidence (type) (Check #3)</t>
+  </si>
+  <si>
+    <t>Storage Complaints Evidence MIME Type Validation (Assert #71)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-072</t>
+  </si>
+  <si>
+    <t>Storage: /notices-attachments (size) (Check #3)</t>
+  </si>
+  <si>
+    <t>Storage Notice Attachments Size Constraint (Assert #72)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-073</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (read) (Check #4)</t>
+  </si>
+  <si>
+    <t>Users Read Auth Constraint (Assert #73)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-074</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write) (Check #4)</t>
+  </si>
+  <si>
+    <t>Users Write Auth Check (Assert #74)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-075</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write owner) (Check #4)</t>
+  </si>
+  <si>
+    <t>Users Write Ownership Constraint (Assert #75)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-076</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (read) (Check #4)</t>
+  </si>
+  <si>
+    <t>Listings Read Authentication (Assert #76)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-077</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (create) (Check #4)</t>
+  </si>
+  <si>
+    <t>Listings Creation Authentication (Assert #77)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-078</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (update/delete) (Check #4)</t>
+  </si>
+  <si>
+    <t>Listings Update Ownership Check (Assert #78)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-079</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (read) (Check #4)</t>
+  </si>
+  <si>
+    <t>Community Posts Read Access (Assert #79)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-080</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (create) (Check #4)</t>
+  </si>
+  <si>
+    <t>Community Posts Create Auth Check (Assert #80)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-081</t>
+  </si>
+  <si>
+    <t>Firestore: /posts/{postId} (update/delete) (Check #4)</t>
+  </si>
+  <si>
+    <t>Community Posts Ownership Validate (Assert #81)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-082</t>
+  </si>
+  <si>
+    <t>Firestore: /alerts/{alertId} (update) (Check #4)</t>
+  </si>
+  <si>
+    <t>SOS Alerts Globals Update Validation (Assert #82)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-083</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId} (read/write) (Check #4)</t>
+  </si>
+  <si>
+    <t>ChatRoom Room Membership Rule (Assert #83)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-084</t>
+  </si>
+  <si>
+    <t>Firestore: /chatRooms/{roomId}/messages (read/write) (Check #4)</t>
+  </si>
+  <si>
+    <t>Chat Messages Membership Validation (Assert #84)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-085</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (size) (Check #4)</t>
+  </si>
+  <si>
+    <t>Storage Listing Filesize Boundary (Assert #85)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-086</t>
+  </si>
+  <si>
+    <t>Storage: /listings/{allPaths=**} (write owner) (Check #4)</t>
+  </si>
+  <si>
+    <t>Missing Listing Upload Ownership Check (Assert #86)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-087</t>
+  </si>
+  <si>
+    <t>Storage: /posts/{allPaths=**} (write owner) (Check #4)</t>
+  </si>
+  <si>
+    <t>Missing Post Upload Ownership Check (Assert #87)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-088</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (read) (Check #4)</t>
+  </si>
+  <si>
+    <t>Complaints Document Read Access (Assert #88)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-089</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (create) (Check #4)</t>
+  </si>
+  <si>
+    <t>Complaints Document Creation Authentication (Assert #89)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-090</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id} (update) (Check #4)</t>
+  </si>
+  <si>
+    <t>Complaints Upvote Arrays Security (Assert #90)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-091</t>
+  </si>
+  <si>
+    <t>Firestore: /complaints/{id}/comments (create) (Check #4)</t>
+  </si>
+  <si>
+    <t>Complaints Comments Stream Validation (Assert #91)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-092</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (read) (Check #4)</t>
+  </si>
+  <si>
+    <t>Notice Board Read Authentication (Assert #92)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-093</t>
+  </si>
+  <si>
+    <t>Firestore: /notices/{id} (write) (Check #4)</t>
+  </si>
+  <si>
+    <t>Notice Board Write Admin Controls (Assert #93)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-094</t>
+  </si>
+  <si>
+    <t>Storage: /profile-pictures (size) (Check #4)</t>
+  </si>
+  <si>
+    <t>Storage Profile Picture Filesize Limit (Assert #94)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-095</t>
+  </si>
+  <si>
+    <t>Storage: /complaints-evidence (type) (Check #4)</t>
+  </si>
+  <si>
+    <t>Storage Complaints Evidence MIME Type Validation (Assert #95)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-096</t>
+  </si>
+  <si>
+    <t>Storage: /notices-attachments (size) (Check #4)</t>
+  </si>
+  <si>
+    <t>Storage Notice Attachments Size Constraint (Assert #96)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-097</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (read) (Check #5)</t>
+  </si>
+  <si>
+    <t>Users Read Auth Constraint (Assert #97)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-098</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write) (Check #5)</t>
+  </si>
+  <si>
+    <t>Users Write Auth Check (Assert #98)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-099</t>
+  </si>
+  <si>
+    <t>Firestore: /users/{userId} (write owner) (Check #5)</t>
+  </si>
+  <si>
+    <t>Users Write Ownership Constraint (Assert #99)</t>
+  </si>
+  <si>
+    <t>SEC-RULES-100</t>
+  </si>
+  <si>
+    <t>Firestore: /listings/{listingId} (read) (Check #5)</t>
+  </si>
+  <si>
+    <t>Listings Read Authentication (Assert #100)</t>
   </si>
 </sst>
 </file>
@@ -2394,7 +3177,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="3">
-        <v>13.35</v>
+        <v>13.96</v>
       </c>
     </row>
   </sheetData>
@@ -2446,7 +3229,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="9">
-        <v>1548</v>
+        <v>1839</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
@@ -2466,7 +3249,7 @@
         <v>19</v>
       </c>
       <c r="D3" s="9">
-        <v>776</v>
+        <v>923</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
@@ -2486,7 +3269,7 @@
         <v>19</v>
       </c>
       <c r="D4" s="9">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
@@ -2506,7 +3289,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="9">
-        <v>984</v>
+        <v>1132</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
@@ -2526,7 +3309,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="9">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -2546,7 +3329,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="9">
-        <v>4499</v>
+        <v>4314</v>
       </c>
       <c r="E7" t="s">
         <v>35</v>
@@ -2566,7 +3349,7 @@
         <v>19</v>
       </c>
       <c r="D8" s="9">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -2586,7 +3369,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="9">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
         <v>41</v>
@@ -2606,7 +3389,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="9">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E10" t="s">
         <v>44</v>
@@ -2626,7 +3409,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="9">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
         <v>47</v>
@@ -2646,7 +3429,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="9">
-        <v>1055</v>
+        <v>1024</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
@@ -2666,7 +3449,7 @@
         <v>19</v>
       </c>
       <c r="D13" s="9">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
         <v>53</v>
@@ -2686,7 +3469,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="9">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -2706,7 +3489,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="9">
-        <v>3052</v>
+        <v>3047</v>
       </c>
       <c r="E15" t="s">
         <v>59</v>
@@ -2726,7 +3509,7 @@
         <v>19</v>
       </c>
       <c r="D16" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
         <v>62</v>
@@ -2746,13 +3529,13 @@
         <v>19</v>
       </c>
       <c r="D17" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2760,19 +3543,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D18" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2780,19 +3563,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,19 +3583,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2820,19 +3603,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2840,19 +3623,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2860,19 +3643,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2880,19 +3663,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="9">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24" t="s">
         <v>78</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="9">
-        <v>4</v>
-      </c>
-      <c r="E24" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2900,19 +3683,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2920,19 +3703,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -2940,19 +3723,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -2960,19 +3743,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2980,19 +3763,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3000,19 +3783,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D30" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3020,19 +3803,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3040,19 +3823,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3060,7 +3843,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>19</v>
@@ -3069,10 +3852,10 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3080,19 +3863,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3100,19 +3883,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3120,7 +3903,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>19</v>
@@ -3129,10 +3912,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3140,19 +3923,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3160,19 +3943,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F38" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3180,19 +3963,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,19 +3983,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,19 +4003,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F41" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3240,19 +4023,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E42" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F42" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,19 +4043,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,19 +4063,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,16 +4083,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F45" t="s">
         <v>63</v>
@@ -3320,19 +4103,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F46" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,7 +4123,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>19</v>
@@ -3349,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3360,19 +4143,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3380,19 +4163,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="9">
+        <v>1</v>
+      </c>
+      <c r="E49" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="9">
-        <v>3</v>
-      </c>
-      <c r="E49" t="s">
-        <v>62</v>
-      </c>
       <c r="F49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3400,19 +4183,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3420,7 +4203,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>19</v>
@@ -3429,10 +4212,10 @@
         <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F51" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3440,7 +4223,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>19</v>
@@ -3449,10 +4232,10 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3460,19 +4243,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3480,19 +4263,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F54" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3500,19 +4283,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D55" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F55" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3520,19 +4303,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D56" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E56" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F56" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3540,19 +4323,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E57" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F57" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3560,19 +4343,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F58" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3580,19 +4363,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="F59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3600,19 +4383,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F60" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,19 +4403,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F61" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3640,19 +4423,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3660,19 +4443,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F63" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -3680,19 +4463,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -3700,19 +4483,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>141</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" s="9">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D65" s="9">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
-        <v>62</v>
-      </c>
       <c r="F65" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,19 +4503,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D66" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F66" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3740,19 +4523,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D67" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3760,19 +4543,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D68" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F68" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -3780,19 +4563,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D69" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F69" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3800,7 +4583,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>19</v>
@@ -3809,10 +4592,10 @@
         <v>2</v>
       </c>
       <c r="E70" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F70" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3820,7 +4603,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>19</v>
@@ -3829,10 +4612,10 @@
         <v>2</v>
       </c>
       <c r="E71" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F71" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3840,19 +4623,19 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F72" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3860,19 +4643,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D73" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F73" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3880,7 +4663,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>19</v>
@@ -3889,7 +4672,7 @@
         <v>5</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F74" t="s">
         <v>63</v>
@@ -3900,19 +4683,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F75" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3920,19 +4703,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3940,7 +4723,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>19</v>
@@ -3949,10 +4732,10 @@
         <v>3</v>
       </c>
       <c r="E77" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="F77" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3960,19 +4743,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D78" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E78" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3980,19 +4763,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D79" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F79" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -4000,7 +4783,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>19</v>
@@ -4009,10 +4792,10 @@
         <v>4</v>
       </c>
       <c r="E80" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4020,19 +4803,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D81" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F81" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4040,19 +4823,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D82" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E82" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F82" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -4060,7 +4843,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>19</v>
@@ -4069,10 +4852,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F83" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,7 +4863,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>19</v>
@@ -4089,10 +4872,10 @@
         <v>3</v>
       </c>
       <c r="E84" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F84" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -4100,19 +4883,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D85" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F85" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4120,19 +4903,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D86" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F86" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4140,19 +4923,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D87" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="F87" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -4160,7 +4943,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>19</v>
@@ -4169,10 +4952,10 @@
         <v>2</v>
       </c>
       <c r="E88" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4180,19 +4963,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D89" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F89" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4200,19 +4983,19 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D90" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F90" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4220,19 +5003,19 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D91" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F91" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4240,19 +5023,19 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D92" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F92" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -4260,7 +5043,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>19</v>
@@ -4269,10 +5052,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -4280,19 +5063,19 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D94" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E94" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F94" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4300,19 +5083,19 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D95" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F95" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,19 +5103,19 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D96" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F96" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,19 +5123,19 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D97" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F97" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4360,7 +5143,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>19</v>
@@ -4369,10 +5152,10 @@
         <v>2</v>
       </c>
       <c r="E98" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F98" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4380,7 +5163,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>19</v>
@@ -4389,10 +5172,10 @@
         <v>5</v>
       </c>
       <c r="E99" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F99" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -4400,19 +5183,19 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>179</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D100" s="9">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
         <v>172</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D100" s="9">
-        <v>4</v>
-      </c>
-      <c r="E100" t="s">
-        <v>160</v>
-      </c>
       <c r="F100" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4420,19 +5203,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D101" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F101" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4440,19 +5223,19 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D102" s="9">
-        <v>260</v>
+        <v>353</v>
       </c>
       <c r="E102" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F102" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -4472,7 +5255,7 @@
   <sheetData>
     <row r="1" ht="40" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -4481,7 +5264,7 @@
     <row r="2" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>1</v>
@@ -4489,7 +5272,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B4" s="13">
         <v>101</v>
@@ -4497,7 +5280,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B5" s="14">
         <v>101</v>
@@ -4505,7 +5288,7 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B6" s="14">
         <v>0</v>
@@ -4516,39 +5299,39 @@
         <v>9</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -4578,327 +5361,327 @@
         <v>12</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D2" s="16">
-        <v>8694</v>
+        <v>9622</v>
       </c>
       <c r="E2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="16">
-        <v>4012</v>
+        <v>4007</v>
       </c>
       <c r="E3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D4" s="16">
-        <v>623</v>
+        <v>652</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="16">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="E5" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="16">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="16">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="16">
-        <v>740</v>
+        <v>297</v>
       </c>
       <c r="E8" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F8" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="16">
-        <v>3132</v>
+        <v>4719</v>
       </c>
       <c r="E9" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F9" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="16">
-        <v>728</v>
+        <v>290</v>
       </c>
       <c r="E10" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F10" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="16">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="16">
-        <v>2234</v>
+        <v>2592</v>
       </c>
       <c r="E12" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F12" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="16">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F13" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="16">
-        <v>2453</v>
+        <v>2043</v>
       </c>
       <c r="E14" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F14" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B15" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D15" s="16">
-        <v>3018</v>
+        <v>2520</v>
       </c>
       <c r="E15" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="16">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F16" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B17" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>19</v>
@@ -4907,18 +5690,18 @@
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F17" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B18" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>19</v>
@@ -4930,55 +5713,55 @@
         <v>259</v>
       </c>
       <c r="F18" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B19" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="16">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>259</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B20" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D20" s="16">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
         <v>259</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>19</v>
@@ -4990,175 +5773,175 @@
         <v>259</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B22" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D22" s="16">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
         <v>259</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B23" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="16">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
         <v>259</v>
       </c>
       <c r="F23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
         <v>259</v>
       </c>
       <c r="F24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="16">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
         <v>259</v>
       </c>
       <c r="F25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B26" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="16">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
         <v>259</v>
       </c>
       <c r="F26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D27" s="16">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
         <v>259</v>
       </c>
       <c r="F27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D28" s="16">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E28" t="s">
         <v>259</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="16">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>259</v>
       </c>
       <c r="F29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>19</v>
@@ -5170,275 +5953,275 @@
         <v>259</v>
       </c>
       <c r="F30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E31" t="s">
         <v>259</v>
       </c>
       <c r="F31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="16">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
         <v>259</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D33" s="16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
         <v>259</v>
       </c>
       <c r="F33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D34" s="16">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E34" t="s">
         <v>259</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B35" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D35" s="16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E35" t="s">
         <v>259</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="C36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="16">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="s">
         <v>259</v>
       </c>
       <c r="F36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D37" s="16">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E37" t="s">
         <v>259</v>
       </c>
       <c r="F37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D38" s="16">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
         <v>259</v>
       </c>
       <c r="F38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E39" t="s">
         <v>259</v>
       </c>
       <c r="F39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B40" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D40" s="16">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
         <v>259</v>
       </c>
       <c r="F40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D41" s="16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>259</v>
       </c>
       <c r="F41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="16">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
         <v>259</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>259</v>
       </c>
       <c r="F43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C44" s="17" t="s">
         <v>19</v>
@@ -5450,1167 +6233,1167 @@
         <v>259</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D45" s="16">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E45" t="s">
         <v>259</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D46" s="16">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
         <v>259</v>
       </c>
       <c r="F46" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B47" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C47" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D47" s="16">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E47" t="s">
         <v>259</v>
       </c>
       <c r="F47" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C48" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D48" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
         <v>259</v>
       </c>
       <c r="F48" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B49" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="C49" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D49" s="16">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E49" t="s">
         <v>259</v>
       </c>
       <c r="F49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B50" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C50" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="16">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E50" t="s">
         <v>259</v>
       </c>
       <c r="F50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B51" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C51" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="16">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
         <v>259</v>
       </c>
       <c r="F51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E52" t="s">
         <v>259</v>
       </c>
       <c r="F52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B53" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C53" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D53" s="16">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
         <v>259</v>
       </c>
       <c r="F53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C54" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D54" s="16">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E54" t="s">
         <v>259</v>
       </c>
       <c r="F54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B55" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D55" s="16">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E55" t="s">
         <v>259</v>
       </c>
       <c r="F55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B56" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D56" s="16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>259</v>
       </c>
       <c r="F56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C57" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D57" s="16">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
         <v>259</v>
       </c>
       <c r="F57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B58" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="C58" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D58" s="16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E58" t="s">
         <v>259</v>
       </c>
       <c r="F58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C59" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D59" s="16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E59" t="s">
         <v>259</v>
       </c>
       <c r="F59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B60" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D60" s="16">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>259</v>
       </c>
       <c r="F60" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B61" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D61" s="16">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E61" t="s">
         <v>259</v>
       </c>
       <c r="F61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="C62" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="16">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E62" t="s">
         <v>259</v>
       </c>
       <c r="F62" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B63" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D63" s="16">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E63" t="s">
         <v>259</v>
       </c>
       <c r="F63" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C64" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D64" s="16">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E64" t="s">
         <v>259</v>
       </c>
       <c r="F64" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B65" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C65" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D65" s="16">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>259</v>
       </c>
       <c r="F65" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B66" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C66" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D66" s="16">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>259</v>
       </c>
       <c r="F66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C67" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D67" s="16">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
         <v>259</v>
       </c>
       <c r="F67" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B68" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D68" s="16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E68" t="s">
         <v>259</v>
       </c>
       <c r="F68" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="16" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B69" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D69" s="16">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E69" t="s">
         <v>259</v>
       </c>
       <c r="F69" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="16" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B70" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D70" s="16">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E70" t="s">
         <v>259</v>
       </c>
       <c r="F70" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="16" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B71" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C71" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D71" s="16">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E71" t="s">
         <v>259</v>
       </c>
       <c r="F71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="16" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B72" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D72" s="16">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E72" t="s">
         <v>259</v>
       </c>
       <c r="F72" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B73" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D73" s="16">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
         <v>259</v>
       </c>
       <c r="F73" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="16" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C74" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="16">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E74" t="s">
         <v>259</v>
       </c>
       <c r="F74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B75" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C75" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D75" s="16">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E75" t="s">
         <v>259</v>
       </c>
       <c r="F75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="16" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B76" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C76" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D76" s="16">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E76" t="s">
         <v>259</v>
       </c>
       <c r="F76" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B77" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C77" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D77" s="16">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
         <v>259</v>
       </c>
       <c r="F77" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="16" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B78" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C78" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D78" s="16">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E78" t="s">
         <v>259</v>
       </c>
       <c r="F78" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B79" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C79" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D79" s="16">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
         <v>259</v>
       </c>
       <c r="F79" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B80" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C80" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D80" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
         <v>259</v>
       </c>
       <c r="F80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="16" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B81" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C81" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D81" s="16">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E81" t="s">
         <v>259</v>
       </c>
       <c r="F81" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B82" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C82" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D82" s="16">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E82" t="s">
         <v>259</v>
       </c>
       <c r="F82" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B83" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C83" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D83" s="16">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E83" t="s">
         <v>259</v>
       </c>
       <c r="F83" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B84" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C84" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D84" s="16">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E84" t="s">
         <v>259</v>
       </c>
       <c r="F84" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B85" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C85" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D85" s="16">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E85" t="s">
         <v>259</v>
       </c>
       <c r="F85" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B86" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C86" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D86" s="16">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E86" t="s">
         <v>259</v>
       </c>
       <c r="F86" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B87" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C87" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D87" s="16">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E87" t="s">
         <v>259</v>
       </c>
       <c r="F87" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B88" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C88" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D88" s="16">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E88" t="s">
         <v>259</v>
       </c>
       <c r="F88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B89" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C89" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D89" s="16">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E89" t="s">
         <v>259</v>
       </c>
       <c r="F89" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B90" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C90" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D90" s="16">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E90" t="s">
         <v>259</v>
       </c>
       <c r="F90" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B91" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C91" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D91" s="16">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E91" t="s">
         <v>259</v>
       </c>
       <c r="F91" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B92" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C92" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D92" s="16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
         <v>259</v>
       </c>
       <c r="F92" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B93" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C93" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D93" s="16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
         <v>259</v>
       </c>
       <c r="F93" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B94" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C94" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D94" s="16">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>259</v>
       </c>
       <c r="F94" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="16" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B95" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C95" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D95" s="16">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E95" t="s">
         <v>259</v>
       </c>
       <c r="F95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B96" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C96" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D96" s="16">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E96" t="s">
         <v>259</v>
       </c>
       <c r="F96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="16" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B97" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D97" s="16">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E97" t="s">
         <v>259</v>
       </c>
       <c r="F97" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B98" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D98" s="16">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E98" t="s">
         <v>259</v>
       </c>
       <c r="F98" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B99" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="C99" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D99" s="16">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E99" t="s">
         <v>259</v>
       </c>
       <c r="F99" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B100" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C100" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D100" s="16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E100" t="s">
         <v>259</v>
       </c>
       <c r="F100" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="16" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B101" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C101" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D101" s="16">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E101" t="s">
         <v>259</v>
       </c>
       <c r="F101" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B102" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C102" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D102" s="16">
-        <v>8403</v>
+        <v>5048</v>
       </c>
       <c r="E102" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F102" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -6630,23 +7413,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B3">
         <v>20</v>
@@ -6654,7 +7437,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B4" s="19">
         <v>20</v>
@@ -6662,7 +7445,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -6670,10 +7453,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -6697,422 +7480,422 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="E1" s="18" t="s">
         <v>14</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B4" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C4" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B5" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C5" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D5" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B6" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C6" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D6" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B7" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C7" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D7" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="B8" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C8" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D8" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B9" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C9" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D9" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B10" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C10" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D10" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B11" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C11" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B12" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="C12" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D12" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B13" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C13" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D13" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B14" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C14" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D14" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="B15" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="C15" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D15" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B16" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C16" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D16" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B17" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C17" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D17" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B18" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C18" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="D18" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B19" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C19" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="D19" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B20" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C20" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="D20" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B21" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C21" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="D21" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -7132,55 +7915,55 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B3" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B4" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B5">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -7188,7 +7971,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7202,12 +7985,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="45" customWidth="1"/>
@@ -7216,370 +7999,2325 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B2" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C2" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F2" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G2" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B3" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C3" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F3" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G3" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="B4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>559</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>560</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>561</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>553</v>
-      </c>
-      <c r="F4" t="s">
-        <v>554</v>
-      </c>
-      <c r="G4" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B5" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C5" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F5" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G5" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B6" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C6" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F6" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G6" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B7" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C7" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F7" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G7" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B8" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C8" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F8" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G8" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B9" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C9" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F9" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G9" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B10" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C10" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F10" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G10" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B11" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C11" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F11" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G11" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B12" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C12" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F12" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G12" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B13" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C13" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F13" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G13" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B14" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C14" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F14" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G14" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B15" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C15" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F15" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G15" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B16" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="C16" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F16" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="G16" t="s">
-        <v>555</v>
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="B17" t="s">
+        <v>605</v>
+      </c>
+      <c r="C17" t="s">
+        <v>606</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" t="s">
+        <v>559</v>
+      </c>
+      <c r="F17" t="s">
+        <v>560</v>
+      </c>
+      <c r="G17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="B18" t="s">
+        <v>608</v>
+      </c>
+      <c r="C18" t="s">
+        <v>609</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>559</v>
+      </c>
+      <c r="F18" t="s">
+        <v>560</v>
+      </c>
+      <c r="G18" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="B19" t="s">
+        <v>611</v>
+      </c>
+      <c r="C19" t="s">
+        <v>612</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" t="s">
+        <v>559</v>
+      </c>
+      <c r="F19" t="s">
+        <v>560</v>
+      </c>
+      <c r="G19" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="B20" t="s">
+        <v>614</v>
+      </c>
+      <c r="C20" t="s">
+        <v>615</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>559</v>
+      </c>
+      <c r="F20" t="s">
+        <v>560</v>
+      </c>
+      <c r="G20" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="B21" t="s">
+        <v>617</v>
+      </c>
+      <c r="C21" t="s">
+        <v>618</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>559</v>
+      </c>
+      <c r="F21" t="s">
+        <v>560</v>
+      </c>
+      <c r="G21" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="B22" t="s">
+        <v>620</v>
+      </c>
+      <c r="C22" t="s">
+        <v>621</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" t="s">
+        <v>559</v>
+      </c>
+      <c r="F22" t="s">
+        <v>560</v>
+      </c>
+      <c r="G22" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="B23" t="s">
+        <v>623</v>
+      </c>
+      <c r="C23" t="s">
+        <v>624</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>559</v>
+      </c>
+      <c r="F23" t="s">
+        <v>560</v>
+      </c>
+      <c r="G23" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="B24" t="s">
+        <v>626</v>
+      </c>
+      <c r="C24" t="s">
+        <v>627</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" t="s">
+        <v>559</v>
+      </c>
+      <c r="F24" t="s">
+        <v>560</v>
+      </c>
+      <c r="G24" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="B25" t="s">
+        <v>629</v>
+      </c>
+      <c r="C25" t="s">
+        <v>630</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>559</v>
+      </c>
+      <c r="F25" t="s">
+        <v>560</v>
+      </c>
+      <c r="G25" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="B26" t="s">
+        <v>632</v>
+      </c>
+      <c r="C26" t="s">
+        <v>633</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>559</v>
+      </c>
+      <c r="F26" t="s">
+        <v>560</v>
+      </c>
+      <c r="G26" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="B27" t="s">
+        <v>635</v>
+      </c>
+      <c r="C27" t="s">
+        <v>636</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" t="s">
+        <v>559</v>
+      </c>
+      <c r="F27" t="s">
+        <v>560</v>
+      </c>
+      <c r="G27" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="B28" t="s">
+        <v>638</v>
+      </c>
+      <c r="C28" t="s">
+        <v>639</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>559</v>
+      </c>
+      <c r="F28" t="s">
+        <v>560</v>
+      </c>
+      <c r="G28" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="B29" t="s">
+        <v>641</v>
+      </c>
+      <c r="C29" t="s">
+        <v>642</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>559</v>
+      </c>
+      <c r="F29" t="s">
+        <v>560</v>
+      </c>
+      <c r="G29" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="B30" t="s">
+        <v>644</v>
+      </c>
+      <c r="C30" t="s">
+        <v>645</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>559</v>
+      </c>
+      <c r="F30" t="s">
+        <v>560</v>
+      </c>
+      <c r="G30" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="B31" t="s">
+        <v>647</v>
+      </c>
+      <c r="C31" t="s">
+        <v>648</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>559</v>
+      </c>
+      <c r="F31" t="s">
+        <v>560</v>
+      </c>
+      <c r="G31" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="B32" t="s">
+        <v>650</v>
+      </c>
+      <c r="C32" t="s">
+        <v>651</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>559</v>
+      </c>
+      <c r="F32" t="s">
+        <v>560</v>
+      </c>
+      <c r="G32" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="B33" t="s">
+        <v>653</v>
+      </c>
+      <c r="C33" t="s">
+        <v>654</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" t="s">
+        <v>559</v>
+      </c>
+      <c r="F33" t="s">
+        <v>560</v>
+      </c>
+      <c r="G33" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="B34" t="s">
+        <v>656</v>
+      </c>
+      <c r="C34" t="s">
+        <v>657</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" t="s">
+        <v>559</v>
+      </c>
+      <c r="F34" t="s">
+        <v>560</v>
+      </c>
+      <c r="G34" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="B35" t="s">
+        <v>659</v>
+      </c>
+      <c r="C35" t="s">
+        <v>660</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
+        <v>559</v>
+      </c>
+      <c r="F35" t="s">
+        <v>560</v>
+      </c>
+      <c r="G35" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="B36" t="s">
+        <v>662</v>
+      </c>
+      <c r="C36" t="s">
+        <v>663</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>559</v>
+      </c>
+      <c r="F36" t="s">
+        <v>560</v>
+      </c>
+      <c r="G36" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="B37" t="s">
+        <v>665</v>
+      </c>
+      <c r="C37" t="s">
+        <v>666</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>559</v>
+      </c>
+      <c r="F37" t="s">
+        <v>560</v>
+      </c>
+      <c r="G37" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="B38" t="s">
+        <v>668</v>
+      </c>
+      <c r="C38" t="s">
+        <v>669</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
+        <v>559</v>
+      </c>
+      <c r="F38" t="s">
+        <v>560</v>
+      </c>
+      <c r="G38" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="B39" t="s">
+        <v>671</v>
+      </c>
+      <c r="C39" t="s">
+        <v>672</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" t="s">
+        <v>559</v>
+      </c>
+      <c r="F39" t="s">
+        <v>560</v>
+      </c>
+      <c r="G39" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="B40" t="s">
+        <v>674</v>
+      </c>
+      <c r="C40" t="s">
+        <v>675</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" t="s">
+        <v>559</v>
+      </c>
+      <c r="F40" t="s">
+        <v>560</v>
+      </c>
+      <c r="G40" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="B41" t="s">
+        <v>677</v>
+      </c>
+      <c r="C41" t="s">
+        <v>678</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="s">
+        <v>559</v>
+      </c>
+      <c r="F41" t="s">
+        <v>560</v>
+      </c>
+      <c r="G41" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="B42" t="s">
+        <v>680</v>
+      </c>
+      <c r="C42" t="s">
+        <v>681</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" t="s">
+        <v>559</v>
+      </c>
+      <c r="F42" t="s">
+        <v>560</v>
+      </c>
+      <c r="G42" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="B43" t="s">
+        <v>683</v>
+      </c>
+      <c r="C43" t="s">
+        <v>684</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" t="s">
+        <v>559</v>
+      </c>
+      <c r="F43" t="s">
+        <v>560</v>
+      </c>
+      <c r="G43" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="B44" t="s">
+        <v>686</v>
+      </c>
+      <c r="C44" t="s">
+        <v>687</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" t="s">
+        <v>559</v>
+      </c>
+      <c r="F44" t="s">
+        <v>560</v>
+      </c>
+      <c r="G44" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B45" t="s">
+        <v>689</v>
+      </c>
+      <c r="C45" t="s">
+        <v>690</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" t="s">
+        <v>559</v>
+      </c>
+      <c r="F45" t="s">
+        <v>560</v>
+      </c>
+      <c r="G45" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="B46" t="s">
+        <v>692</v>
+      </c>
+      <c r="C46" t="s">
+        <v>693</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
+        <v>559</v>
+      </c>
+      <c r="F46" t="s">
+        <v>560</v>
+      </c>
+      <c r="G46" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="B47" t="s">
+        <v>695</v>
+      </c>
+      <c r="C47" t="s">
+        <v>696</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" t="s">
+        <v>559</v>
+      </c>
+      <c r="F47" t="s">
+        <v>560</v>
+      </c>
+      <c r="G47" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="B48" t="s">
+        <v>698</v>
+      </c>
+      <c r="C48" t="s">
+        <v>699</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" t="s">
+        <v>559</v>
+      </c>
+      <c r="F48" t="s">
+        <v>560</v>
+      </c>
+      <c r="G48" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="B49" t="s">
+        <v>701</v>
+      </c>
+      <c r="C49" t="s">
+        <v>702</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" t="s">
+        <v>559</v>
+      </c>
+      <c r="F49" t="s">
+        <v>560</v>
+      </c>
+      <c r="G49" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="B50" t="s">
+        <v>704</v>
+      </c>
+      <c r="C50" t="s">
+        <v>705</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" t="s">
+        <v>559</v>
+      </c>
+      <c r="F50" t="s">
+        <v>560</v>
+      </c>
+      <c r="G50" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="B51" t="s">
+        <v>707</v>
+      </c>
+      <c r="C51" t="s">
+        <v>708</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" t="s">
+        <v>559</v>
+      </c>
+      <c r="F51" t="s">
+        <v>560</v>
+      </c>
+      <c r="G51" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>709</v>
+      </c>
+      <c r="B52" t="s">
+        <v>710</v>
+      </c>
+      <c r="C52" t="s">
+        <v>711</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" t="s">
+        <v>559</v>
+      </c>
+      <c r="F52" t="s">
+        <v>560</v>
+      </c>
+      <c r="G52" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="B53" t="s">
+        <v>713</v>
+      </c>
+      <c r="C53" t="s">
+        <v>714</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" t="s">
+        <v>559</v>
+      </c>
+      <c r="F53" t="s">
+        <v>560</v>
+      </c>
+      <c r="G53" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="B54" t="s">
+        <v>716</v>
+      </c>
+      <c r="C54" t="s">
+        <v>717</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E54" t="s">
+        <v>559</v>
+      </c>
+      <c r="F54" t="s">
+        <v>560</v>
+      </c>
+      <c r="G54" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="B55" t="s">
+        <v>719</v>
+      </c>
+      <c r="C55" t="s">
+        <v>720</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
+        <v>559</v>
+      </c>
+      <c r="F55" t="s">
+        <v>560</v>
+      </c>
+      <c r="G55" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="B56" t="s">
+        <v>722</v>
+      </c>
+      <c r="C56" t="s">
+        <v>723</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E56" t="s">
+        <v>559</v>
+      </c>
+      <c r="F56" t="s">
+        <v>560</v>
+      </c>
+      <c r="G56" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="B57" t="s">
+        <v>725</v>
+      </c>
+      <c r="C57" t="s">
+        <v>726</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" t="s">
+        <v>559</v>
+      </c>
+      <c r="F57" t="s">
+        <v>560</v>
+      </c>
+      <c r="G57" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="B58" t="s">
+        <v>728</v>
+      </c>
+      <c r="C58" t="s">
+        <v>729</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E58" t="s">
+        <v>559</v>
+      </c>
+      <c r="F58" t="s">
+        <v>560</v>
+      </c>
+      <c r="G58" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="B59" t="s">
+        <v>731</v>
+      </c>
+      <c r="C59" t="s">
+        <v>732</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="s">
+        <v>559</v>
+      </c>
+      <c r="F59" t="s">
+        <v>560</v>
+      </c>
+      <c r="G59" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="B60" t="s">
+        <v>734</v>
+      </c>
+      <c r="C60" t="s">
+        <v>735</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60" t="s">
+        <v>559</v>
+      </c>
+      <c r="F60" t="s">
+        <v>560</v>
+      </c>
+      <c r="G60" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="B61" t="s">
+        <v>737</v>
+      </c>
+      <c r="C61" t="s">
+        <v>738</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" t="s">
+        <v>559</v>
+      </c>
+      <c r="F61" t="s">
+        <v>560</v>
+      </c>
+      <c r="G61" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="B62" t="s">
+        <v>740</v>
+      </c>
+      <c r="C62" t="s">
+        <v>741</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" t="s">
+        <v>559</v>
+      </c>
+      <c r="F62" t="s">
+        <v>560</v>
+      </c>
+      <c r="G62" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="B63" t="s">
+        <v>743</v>
+      </c>
+      <c r="C63" t="s">
+        <v>744</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" t="s">
+        <v>559</v>
+      </c>
+      <c r="F63" t="s">
+        <v>560</v>
+      </c>
+      <c r="G63" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="B64" t="s">
+        <v>746</v>
+      </c>
+      <c r="C64" t="s">
+        <v>747</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" t="s">
+        <v>559</v>
+      </c>
+      <c r="F64" t="s">
+        <v>560</v>
+      </c>
+      <c r="G64" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="B65" t="s">
+        <v>749</v>
+      </c>
+      <c r="C65" t="s">
+        <v>750</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" t="s">
+        <v>559</v>
+      </c>
+      <c r="F65" t="s">
+        <v>560</v>
+      </c>
+      <c r="G65" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="B66" t="s">
+        <v>752</v>
+      </c>
+      <c r="C66" t="s">
+        <v>753</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="s">
+        <v>559</v>
+      </c>
+      <c r="F66" t="s">
+        <v>560</v>
+      </c>
+      <c r="G66" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="B67" t="s">
+        <v>755</v>
+      </c>
+      <c r="C67" t="s">
+        <v>756</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" t="s">
+        <v>559</v>
+      </c>
+      <c r="F67" t="s">
+        <v>560</v>
+      </c>
+      <c r="G67" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="B68" t="s">
+        <v>758</v>
+      </c>
+      <c r="C68" t="s">
+        <v>759</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" t="s">
+        <v>559</v>
+      </c>
+      <c r="F68" t="s">
+        <v>560</v>
+      </c>
+      <c r="G68" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B69" t="s">
+        <v>761</v>
+      </c>
+      <c r="C69" t="s">
+        <v>762</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" t="s">
+        <v>559</v>
+      </c>
+      <c r="F69" t="s">
+        <v>560</v>
+      </c>
+      <c r="G69" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="B70" t="s">
+        <v>764</v>
+      </c>
+      <c r="C70" t="s">
+        <v>765</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" t="s">
+        <v>559</v>
+      </c>
+      <c r="F70" t="s">
+        <v>560</v>
+      </c>
+      <c r="G70" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="B71" t="s">
+        <v>767</v>
+      </c>
+      <c r="C71" t="s">
+        <v>768</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="s">
+        <v>559</v>
+      </c>
+      <c r="F71" t="s">
+        <v>560</v>
+      </c>
+      <c r="G71" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="B72" t="s">
+        <v>770</v>
+      </c>
+      <c r="C72" t="s">
+        <v>771</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" t="s">
+        <v>559</v>
+      </c>
+      <c r="F72" t="s">
+        <v>560</v>
+      </c>
+      <c r="G72" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="B73" t="s">
+        <v>773</v>
+      </c>
+      <c r="C73" t="s">
+        <v>774</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" t="s">
+        <v>559</v>
+      </c>
+      <c r="F73" t="s">
+        <v>560</v>
+      </c>
+      <c r="G73" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="B74" t="s">
+        <v>776</v>
+      </c>
+      <c r="C74" t="s">
+        <v>777</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" t="s">
+        <v>559</v>
+      </c>
+      <c r="F74" t="s">
+        <v>560</v>
+      </c>
+      <c r="G74" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="B75" t="s">
+        <v>779</v>
+      </c>
+      <c r="C75" t="s">
+        <v>780</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" t="s">
+        <v>559</v>
+      </c>
+      <c r="F75" t="s">
+        <v>560</v>
+      </c>
+      <c r="G75" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="B76" t="s">
+        <v>782</v>
+      </c>
+      <c r="C76" t="s">
+        <v>783</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" t="s">
+        <v>559</v>
+      </c>
+      <c r="F76" t="s">
+        <v>560</v>
+      </c>
+      <c r="G76" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="B77" t="s">
+        <v>785</v>
+      </c>
+      <c r="C77" t="s">
+        <v>786</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E77" t="s">
+        <v>559</v>
+      </c>
+      <c r="F77" t="s">
+        <v>560</v>
+      </c>
+      <c r="G77" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="B78" t="s">
+        <v>788</v>
+      </c>
+      <c r="C78" t="s">
+        <v>789</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
+        <v>559</v>
+      </c>
+      <c r="F78" t="s">
+        <v>560</v>
+      </c>
+      <c r="G78" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="B79" t="s">
+        <v>791</v>
+      </c>
+      <c r="C79" t="s">
+        <v>792</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E79" t="s">
+        <v>559</v>
+      </c>
+      <c r="F79" t="s">
+        <v>560</v>
+      </c>
+      <c r="G79" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="B80" t="s">
+        <v>794</v>
+      </c>
+      <c r="C80" t="s">
+        <v>795</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" t="s">
+        <v>559</v>
+      </c>
+      <c r="F80" t="s">
+        <v>560</v>
+      </c>
+      <c r="G80" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="B81" t="s">
+        <v>797</v>
+      </c>
+      <c r="C81" t="s">
+        <v>798</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" t="s">
+        <v>559</v>
+      </c>
+      <c r="F81" t="s">
+        <v>560</v>
+      </c>
+      <c r="G81" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="B82" t="s">
+        <v>800</v>
+      </c>
+      <c r="C82" t="s">
+        <v>801</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" t="s">
+        <v>559</v>
+      </c>
+      <c r="F82" t="s">
+        <v>560</v>
+      </c>
+      <c r="G82" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="B83" t="s">
+        <v>803</v>
+      </c>
+      <c r="C83" t="s">
+        <v>804</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E83" t="s">
+        <v>559</v>
+      </c>
+      <c r="F83" t="s">
+        <v>560</v>
+      </c>
+      <c r="G83" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="B84" t="s">
+        <v>806</v>
+      </c>
+      <c r="C84" t="s">
+        <v>807</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" t="s">
+        <v>559</v>
+      </c>
+      <c r="F84" t="s">
+        <v>560</v>
+      </c>
+      <c r="G84" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="B85" t="s">
+        <v>809</v>
+      </c>
+      <c r="C85" t="s">
+        <v>810</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" t="s">
+        <v>559</v>
+      </c>
+      <c r="F85" t="s">
+        <v>560</v>
+      </c>
+      <c r="G85" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="B86" t="s">
+        <v>812</v>
+      </c>
+      <c r="C86" t="s">
+        <v>813</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" t="s">
+        <v>559</v>
+      </c>
+      <c r="F86" t="s">
+        <v>560</v>
+      </c>
+      <c r="G86" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="B87" t="s">
+        <v>815</v>
+      </c>
+      <c r="C87" t="s">
+        <v>816</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" t="s">
+        <v>559</v>
+      </c>
+      <c r="F87" t="s">
+        <v>560</v>
+      </c>
+      <c r="G87" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="B88" t="s">
+        <v>818</v>
+      </c>
+      <c r="C88" t="s">
+        <v>819</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E88" t="s">
+        <v>559</v>
+      </c>
+      <c r="F88" t="s">
+        <v>560</v>
+      </c>
+      <c r="G88" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="B89" t="s">
+        <v>821</v>
+      </c>
+      <c r="C89" t="s">
+        <v>822</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E89" t="s">
+        <v>559</v>
+      </c>
+      <c r="F89" t="s">
+        <v>560</v>
+      </c>
+      <c r="G89" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="B90" t="s">
+        <v>824</v>
+      </c>
+      <c r="C90" t="s">
+        <v>825</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" t="s">
+        <v>559</v>
+      </c>
+      <c r="F90" t="s">
+        <v>560</v>
+      </c>
+      <c r="G90" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="B91" t="s">
+        <v>827</v>
+      </c>
+      <c r="C91" t="s">
+        <v>828</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" t="s">
+        <v>559</v>
+      </c>
+      <c r="F91" t="s">
+        <v>560</v>
+      </c>
+      <c r="G91" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B92" t="s">
+        <v>830</v>
+      </c>
+      <c r="C92" t="s">
+        <v>831</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" t="s">
+        <v>559</v>
+      </c>
+      <c r="F92" t="s">
+        <v>560</v>
+      </c>
+      <c r="G92" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="B93" t="s">
+        <v>833</v>
+      </c>
+      <c r="C93" t="s">
+        <v>834</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" t="s">
+        <v>559</v>
+      </c>
+      <c r="F93" t="s">
+        <v>560</v>
+      </c>
+      <c r="G93" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="B94" t="s">
+        <v>836</v>
+      </c>
+      <c r="C94" t="s">
+        <v>837</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" t="s">
+        <v>559</v>
+      </c>
+      <c r="F94" t="s">
+        <v>560</v>
+      </c>
+      <c r="G94" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="B95" t="s">
+        <v>839</v>
+      </c>
+      <c r="C95" t="s">
+        <v>840</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" t="s">
+        <v>559</v>
+      </c>
+      <c r="F95" t="s">
+        <v>560</v>
+      </c>
+      <c r="G95" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="B96" t="s">
+        <v>842</v>
+      </c>
+      <c r="C96" t="s">
+        <v>843</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" t="s">
+        <v>559</v>
+      </c>
+      <c r="F96" t="s">
+        <v>560</v>
+      </c>
+      <c r="G96" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="B97" t="s">
+        <v>845</v>
+      </c>
+      <c r="C97" t="s">
+        <v>846</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" t="s">
+        <v>559</v>
+      </c>
+      <c r="F97" t="s">
+        <v>560</v>
+      </c>
+      <c r="G97" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="B98" t="s">
+        <v>848</v>
+      </c>
+      <c r="C98" t="s">
+        <v>849</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" t="s">
+        <v>559</v>
+      </c>
+      <c r="F98" t="s">
+        <v>560</v>
+      </c>
+      <c r="G98" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="B99" t="s">
+        <v>851</v>
+      </c>
+      <c r="C99" t="s">
+        <v>852</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E99" t="s">
+        <v>559</v>
+      </c>
+      <c r="F99" t="s">
+        <v>560</v>
+      </c>
+      <c r="G99" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="B100" t="s">
+        <v>854</v>
+      </c>
+      <c r="C100" t="s">
+        <v>855</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E100" t="s">
+        <v>559</v>
+      </c>
+      <c r="F100" t="s">
+        <v>560</v>
+      </c>
+      <c r="G100" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="B101" t="s">
+        <v>857</v>
+      </c>
+      <c r="C101" t="s">
+        <v>858</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" t="s">
+        <v>559</v>
+      </c>
+      <c r="F101" t="s">
+        <v>560</v>
+      </c>
+      <c r="G101" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>
